--- a/instagram_posts.xlsx
+++ b/instagram_posts.xlsx
@@ -35,6 +35,38 @@
     <t xml:space="preserve">comments_count</t>
   </si>
   <si>
+    <t xml:space="preserve">18350168365239598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📱 Afinal, existe vício em telas?
+A resposta curta é: sim, e o ponto de virada é a perda de controle.
+Quando você não consegue se autorregular, mesmo percebendo prejuízos na saúde, nos estudos ou nas relações, o alerta acende.
+🧠 O que acontece no cérebro?
+As telas ativam o sistema de recompensa (dopamina). Redes sociais e vídeos curtos são feitos para isso. O termo “brain rot” ganhou força justamente para descrever esse consumo excessivo de conteúdos superficiais.
+⚠️ Sinais de alerta:
+• Checar o celular o tempo todo
+• Ansiedade ao ficar offline
+• Trocar sono e momentos reais por tela
+• Irritação ao ser interrompido
+E não é só mental: o uso excessivo também está ligado a sedentarismo, dores na coluna, falta de exposição ao sol e problemas oculares.
+✨ Como retomar o equilíbrio:
+• Regra 20/20 para descansar a visão
+• Definir horários e espaços sem tela
+• Priorizar atividades offline
+💡 A boa notícia: é tratável e reversível. Reduzir o tempo de exposição já ajuda o cérebro a se reorganizar.
+E aí: você controla as telas ou elas controlam você? 👇
+#SaudeMental #DependenciaDigital #BemEstar #BrainRot #VicioEmTelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dN1gHICDS0oQ7kNvwHgD4Zy&amp;_nc_oc=Ado6iKjfwhMgvs4erd9wbyiNXpJ_NN79GOjITXZUfkybBsxrvnxKKQryJgMUBJ4QxwA&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afxr_yaGHZLcIhsdpcS59iS4EQYwiyAdkzwCwqtQe75qHg&amp;oe=69CA2BA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-25T21:00:00+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">18049720682713892</t>
   </si>
   <si>
@@ -48,7 +80,7 @@
     <t xml:space="preserve">CAROUSEL_ALBUM</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwG3ePnf&amp;_nc_oc=AdrC8eVgvWTNoBFg0MUwUTyI9NRxOytBDf8cGyMykz_tSzGkVaqA--QoPmWrFMqiQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfxVm_1ZX351GpGGYWPiA46RRFAcCo7Y94PtzhMEMXIsrw&amp;oe=69CA2E1B</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwEySDv2&amp;_nc_oc=AdqbuAFsVfFvJKgKDdu0XFl9PZbGd6yWQnrXpnMz66iSY4lfxcR0RQ4hgFhELyGAHLk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxzOu7O4AQDNhNemh9tj6xnNdt_xT13dXYkakxLPpHnPg&amp;oe=69CA2E1B</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T13:59:41+0000</t>
@@ -70,7 +102,7 @@
 #IA #SegurançaDigital #Cibersegurança #Inovação #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwHXZt0W&amp;_nc_oc=AdpNG26fHLSire3vRxbm_8tUjtPFMjpAg42ZZcH5zMPsx1zg9hw5S_48Zl-w3HKAbPk&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfyxSdRjiQ6OKz7kuRSyCQ7hNvom5q5oObU3qJTpzV16HQ&amp;oe=69CA0F9A</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwE4w0XM&amp;_nc_oc=Adp8pLPVNcr0CkJ1PWbuTwJSubkKxkBWmxfPqQAxpk59GIv3CqmKOx0eRP1TgnBnmck&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxMYuUiPIEwnG6kVXQvYiH2oMb2iSRBpLccINCpLc6tIw&amp;oe=69CA0F9A</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T21:00:00+0000</t>
@@ -92,7 +124,7 @@
     <t xml:space="preserve">VIDEO</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwHzr5NH&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoyLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ3YXRjaF90aW1lX3MiOjM2MTgsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfwVlrAzwbK3nFbWRBX_T2B-ihT1kqO44DUmxytoT771nw&amp;oe=69CA3274</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwGkukJS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoyLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfwmDil3QERwZrVhUfNHKlzAtomLy0fehyEudywAUf9AhA&amp;oe=69CA3274</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T13:52:41+0000</t>
@@ -119,10 +151,7 @@
 #comunicatibb #Cibersegurança #SegurançaDigital #Tecnologia #DicasDeTI</t>
   </si>
   <si>
-    <t xml:space="preserve">IMAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwG0yq71&amp;_nc_oc=AdrbtlpkbW47_cIf29GPAvh4Q2uENTMdHgkTNditl6UQid3dGBAaU0WdI920HXPdDj4&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_Afya2P8Knygpy9MrxZoPt6ObnkiHZReqTUnfmz3xL4cNLQ&amp;oe=69CA16FC</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwFnMtK4&amp;_nc_oc=AdrcahQc30cHYACaxVJB3--ads6UU4ksFscbZD151Xhhx7WkiY1zAr31I8Zg1bLMSzk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzOJPPi8WlGizVjNCDI_GoCgZH2u9aNgwBQRpMBVzcamw&amp;oe=69CA16FC</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T21:00:00+0000</t>
@@ -141,7 +170,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwEtpNo1&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo1LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsIndhdGNoX3RpbWVfcyI6NzQwNSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfymkY_tpoIuqdJ8R6j3ATZeMsKbtcStqt71LFH8z-k8gQ&amp;oe=69CA1147</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwGVQt1J&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo1LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afz7o_OM8qiApjyYudO74inVroBgXeYwDhOy_VoD9_4WNA&amp;oe=69CA1147</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T12:33:26+0000</t>
@@ -158,7 +187,7 @@
 #RacismoAlgoritmico #InteligenciaArtificial #Diversidade #TecnologiaEtica #InclusãoDigital</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwFlwOSa&amp;_nc_oc=AdrPQnaY8AuCa9YVSPj63xjQNkGfQB0uoYcv4zp0eaYlNK6t_ceIhnYE0ZYj3Nw5z38&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfxK5JpwLfsm0SpRULVdO2zmz5SRYHCpXcm3ssNtd62HPQ&amp;oe=69CA01C4</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwFaoIQ4&amp;_nc_oc=AdpqzmRFOD5U1Ilveh5aSq6UUwdsCqONGuXedraqYf0dq-nclwsCGAFdU6tEmRxCaIw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxJTukKs31ihSur4Mq0Hzr3zduHBbeEydjhZ41ZJdP5kQ&amp;oe=69CA3A04</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-18T16:51:12+0000</t>
@@ -177,7 +206,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwEnbizT&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsIndhdGNoX3RpbWVfcyI6ODg4NCwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfzkMk9N73jI1WdPl4fEQC29hxBc67covWDo9GchxWiZgQ&amp;oe=69CA353F</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwHIZ_88&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfwaQsllX2eOTp9h5pq3RisyYcQCMSj-nhxgDteASScNVQ&amp;oe=69CA353F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T21:00:00+0000</t>
@@ -202,7 +231,7 @@
 #Meta #InteligênciaArtificial #Tecnologia #Inovação #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwHXuAVD&amp;_nc_oc=AdohOCVcRgf9GyftdS4GgtoA4FmquFEmODrP4FrDmYRw3urMuDFibrmIyvcVprcgw8k&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_Afxjvqtwkmr0qO_upS1y08nEXMSDZJZxJpwfyLQgiGmvwQ&amp;oe=69CA0B11</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwE6PYr5&amp;_nc_oc=AdoReFxSOTP8OZpaslIfuouUZDe8Dzx0J8WHfW_jL_VAVmBkCfy2NPub8_KTfgrcrkE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfwZEzLQsr7s2UJpuns6vKwNRAQXf4IHPdzPoYyzjLzHBg&amp;oe=69CA0B11</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T16:36:23+0000</t>
@@ -218,7 +247,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwF5m8wh&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ3YXRjaF90aW1lX3MiOjM3ODAwLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afzddv70f6kJ56GCxix6DW6qFtIVAZkDO3R9G26T84PA6g&amp;oe=69CA0879</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFqNaMb&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfykJgFimn3vB5_X5k3xLf4Wf1XnfPNayIHklOK9UV2aTA&amp;oe=69CA40B9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T21:00:00+0000</t>
@@ -234,7 +263,7 @@
 #ECADigital #DesenvolvimentoDeSoftware #PrivacidadeDeDados #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwGWJq2f&amp;_nc_oc=Ado7pwneZZm4yqnQ1A5JKyEiQx8ZP2yo9T9n6FxllRm9DZpp1sJ8MSzUulIGGmcgusc&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_Afz3QoNBW1lQNJS-zNWsfRZ8tHW86x2PeuO9S78VTboRcA&amp;oe=69CA2BF9</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwG1p8Uv&amp;_nc_oc=Adrgd9iU47lN1un1oXXzzp0SBKx4s0XV8uDkyNB__wWPrrBdpXmoRKBD4fL-msoHW98&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfwNO_4SY0uwBMaAMBz9mDKIb_s9tcIjGzSycu00OM8xHw&amp;oe=69CA2BF9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T16:30:40+0000</t>
@@ -253,7 +282,7 @@
 #Tecnologia #IA #Hardware #SupplyChain Inovaç</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=agFoXPhlYxwQ7kNvwGYWg6j&amp;_nc_oc=AdoIKGPf-nL259KLdzH6J-la7_5RPsL-TiIwwvTw_KWvIdqVXk414eqLiU_oHijkwfI&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfyyE-EsJ_8MD4Itc1BIKdpModuYjVpYeWRXHirrPAhiZA&amp;oe=69CA28F7</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=agFoXPhlYxwQ7kNvwHHFZlB&amp;_nc_oc=AdoIcubrFfcA_vfhr3m_mxkcTbKdm1Zs_xAsNEicrb167vBAOV4rNKYIsjMytQZQUxA&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfwUlYqoT1mFx9San02eMHMgQS5xrIKkFGGYDo9_sAYMkA&amp;oe=69CA28F7</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-12T15:04:46+0000</t>
@@ -270,7 +299,7 @@
 #Cibersegurança #ComunicatIBB #ProteçãoDeDados #SegurançaDigital #SegurançaFinanceira</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwH7g_U_&amp;_nc_oc=Adr-e30kCnew1NyAVvJ4T_n8zK_ANNd0Q6dvEl-fndNYE7yNS-BwqymuXxx3gso2hpA&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfzTar9_R6IyFb6aatH6FFD58qzhzUzxPa25gkDWasRbwA&amp;oe=69CA1FE8</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwG2VIKj&amp;_nc_oc=AdpPWfTCnQLMqnuAAlFBbyqNtHulhWAR7abqMabV4jCkL2VPNcsVwGbzerwcpiovSXI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzLOmPx3P3prmZfAdytpldHq7aD7pmpS5dSgjX3haUpLw&amp;oe=69CA1FE8</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T21:00:00+0000</t>
@@ -289,7 +318,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwHM7bcv&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ3YXRjaF90aW1lX3MiOjI0MjMxLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afx8kFLn0AC40m1beDrIwMuBtxre3Nxss8dsybtXnqE7vw&amp;oe=69CA195E</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwESi3nI&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfyQNvzhRWjuXRotKeZyT6pRasy3olaF4reoi4AxO6fkew&amp;oe=69CA195E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T13:48:44+0000</t>
@@ -307,7 +336,7 @@
 #ColunistasBB #ComunicaTI #CompartilheConhecimento</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwFE5tYp&amp;_nc_oc=AdrD4bramepzxsMhrIC9oUZZunVCanK3xqknv0V7_MyobmmQGyWmfjXrzUSxeB9zGC4&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfylqpjC24skyGWRFdvwZBlSUWQoJDZkNa3tAN1oAEPpkg&amp;oe=69CA0708</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwHd1rUc&amp;_nc_oc=AdrTJaYPclVj0f4ZMooWMdA_px6Ph5HcN6lrxTkGuk6_-trfAdkoCtjfrtMYvLj9dpE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzKup0U34L-RxLW1YVguu4NhKqzbPqBEJUI5pRS0HwfDA&amp;oe=69CA3F48</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-10T17:21:57+0000</t>
@@ -332,7 +361,7 @@
 #GuildasBB #TecnologiaBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwEoHQ3u&amp;_nc_oc=AdqNRQ53O7jgdjRg-BthlqWSTpLG3ETLxli4xA9kYjE3hUYyY0HQR6ASYDXeJXuPATE&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_Afx-K05rFAcUOO9YYAkhffAmg5-rHLLWLcmX-nTT7-onZw&amp;oe=69CA17AE</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwETz-kf&amp;_nc_oc=Ado6HPVYYcZ9-0ZGGzMqv0wkIQfPwPIK1whrt5Xz385pPKQR7-0e4V_wZc_khDkj2jI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afx92_jZ8FeUwM8myJHs4kJEHuokb5Wb9heuyrTEwSGlHg&amp;oe=69CA17AE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-09T13:59:40+0000</t>
@@ -349,7 +378,7 @@
 Feliz Dia Internacional das Mulheres. 💙💛</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwH1KCDD&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ3YXRjaF90aW1lX3MiOjc3Njg4LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfwOXjmbiXFJkrNccXAcE0HLP3QwF1XSC45POZK4b02GPA&amp;oe=69CA0D44</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwGJt03Q&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afy6HzcSsbNLVCWpuhYwkOTDervtapcT2LYNtWKPqODJrg&amp;oe=69CA0D44</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-06T20:47:29+0000</t>
@@ -366,7 +395,7 @@
 #InteligenciaArtificial #Sustentabilidade #Tecnologia #IAVerde #Inovacao ComunicaTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwF3qn-X&amp;_nc_oc=AdqbBJPXc5W5On44PmP32P1LW_3SRmmGoJCg7WlcayT5PqjVP854DM5RsbzX1hIinFA&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_Afwre1wxhMAxYeWr1Ij6EIZqhd_27iv84Jju3boIIkwAmA&amp;oe=69CA2B5F</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwH5r7UV&amp;_nc_oc=AdqVClhmC4cqtgxSL3XUPtIDyABUb6CMOTUn7OLOSkpjUJYsCy7w7AgIJqlTTUhGbmE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfyAiaF6DAo_faFM8WVUBVCIfp9x6Ess7ZdsqsStYvCUMQ&amp;oe=69CA2B5F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-04T17:32:16+0000</t>
@@ -401,7 +430,7 @@
 Salve na agenda e participe! 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwE8cUQW&amp;_nc_oc=Ado8HVcSVM5O7GveYYga3kEhlEkXf4aaJDNOnsoTrNxRaQMGbPZxpd-ip3nipW68hCI&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfzMFU8D96uJPjHAQsessAZdIbsu5O5Bmqe5rAPgCrjgeg&amp;oe=69CA11AE</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwGksi6C&amp;_nc_oc=Adr8iF8K6PgLLMS83XrdIHcupDmSND_8CKQy3JTuUJe8cyMh6RjzwR-ylfw07ONOT7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxkUXivKFqw5cGovPyMghLMH-gclv3CVOMgU5Di66u4Eg&amp;oe=69CA11AE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T18:48:00+0000</t>
@@ -428,7 +457,7 @@
 #MulheresNaTI #Carreira #LiderançaFeminina #Mentoria</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwHnCqbW&amp;_nc_oc=Adp3au-JD4p-kUEzJj0yiFAaauagZdnK7ahbLnPiak2dNblinltjevaZGuLB8jWD5C8&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfxvMhT2o5kLKafwd1Wxhkd5ee1R-pZXirVt3B9lWPSr2Q&amp;oe=69CA11CA</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwGE_8qi&amp;_nc_oc=Adql3TaeguCmttovc5MDkQGohXdx6IX-FFsep97wIZ9TN7rR_81HfofU0cSuF3p4LmU&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzbxhbiFW2UQM4W96irevhTTwD6IYJ_kE1D0cAMvlwRFw&amp;oe=69CA11CA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T16:15:52+0000</t>
@@ -442,7 +471,7 @@
 #ComunicaTI #Ditec #BancoDoBrasil #SomosBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwFX8rOC&amp;_nc_oc=AdrpTLwUYk_QHuMsATnLBN6swE_KhYPlbSSwSJiNfGvXLkwJaL6dwLwiLRlvHNaqt4s&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfzfjhZ3J-h5WvSwYU4UwWw9QSbPNShIanaVwdOKis67rA&amp;oe=69CA26E6</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwGzsXwP&amp;_nc_oc=Adqqfkn33TpL7QVDMVLey0EZjgBvpd2OeMWMANuCdz4CRFpmqw6fmSDNVK8McWe0dJw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxL6VnbZWkzAqwFVyzrj18QjEOcD4jc26qiD3MdhFoaSQ&amp;oe=69CA26E6</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-25T17:10:36+0000</t>
@@ -466,7 +495,7 @@
 #BankingTransformation #Inovação #TecnologiaBB #bancodobrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwFMrAnQ&amp;_nc_oc=AdqRwvrpT2qFWKD3TEMqhPmmOc42oCDg9xA6WyAEyW_sOhRQijx9YsjikIytAudjrPU&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfwXxeLm0M4WWvmupDLqXdNIoYgMrXrbnxK7LMwdvWCLNw&amp;oe=69CA19B5</t>
+    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwFEFEjo&amp;_nc_oc=Adq0reI_EcDevWGiQ41IEnrvQ0O96Z5KxpCtuoZ_6wmTeO5mgsEinRv2UWvRpMKRfhU&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afyt_Pm8yL17rxZj2HtX2m8Lm_gsZVRYFKrb-TBGahTsxA&amp;oe=69CA19B5</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-24T00:45:36+0000</t>
@@ -498,7 +527,7 @@
 #GuildasDaSemana #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-2.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwE4cUjj&amp;_nc_oc=AdpCjAjguDToljEOgCo5XAi3_YA0ePAEFEu7G41Fd7OTGnQYyFlIPmiPauQQKcH3OnQ&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfxsLxiiTmvZn3duM5GYcM2vgho1wpngJMlwuGQGlYJGeA&amp;oe=69CA355E</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwE0URcI&amp;_nc_oc=AdoLb3gFatZ-dA_zenAJgUPLUZAzahnHJMaaVfY-eywkddlBb-3stmVxcsByJbMbCOI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfyWZkeE2e9kxCXJ_vBTh6XhOfCCrKz9iKu5VOIVYCIZZQ&amp;oe=69CA355E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-23T12:27:17+0000</t>
@@ -516,7 +545,7 @@
 #MeninasNaCiência #MulheresNaCiência #MeninasNaCiência #WomenInScience #Inovação</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-1.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwEkGsim&amp;_nc_oc=Adop_1jq_CAU-2CmgubDHjlFoqUGoV42TvnMEHEBqHh937ncCID-7IuFpVyv4pchA4Y&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfwsghsltAQcbnLS_6LLGawt41fJJv2FSAqRbfTxsMvbAw&amp;oe=69CA044F</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwFtOV0v&amp;_nc_oc=AdqckHdbaSEVMKErx4dUWvoBN2SrSw5nW3lYwqbw3IeovRY47uc30pdgmgJLKdSltVw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afx1eK6YfIDiFzK6G02xhfyqS4gztxB8knMnSl_DVSVR4w&amp;oe=69CA3C8F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-11T13:46:50+0000</t>
@@ -538,37 +567,10 @@
 #GuildasDaSemana #Tecnologia #TI #Dados DividaTecnica Analytics IA BancoDoBrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwGhJK7o&amp;_nc_oc=AdrA335wl-lW1czgfNtjX1fWYmXpiJy3_XURt7-NxU_7tZCFiwEOKpBhpRLf9sNLjWY&amp;_nc_zt=23&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;oh=00_AfycA8U-IC7jtXuh5Lpm-0EEl1DpOAQYLcabiAEOUdMKwg&amp;oe=69CA2612</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwEn9AX1&amp;_nc_oc=AdpAcjJf7lXngd2dbxfjiZMR2rnQBZBXD-C88xxyIfC4B4GMUBYJUwV5Llw7CgGwymI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzJ9_OyPdQYKvxbNwAMvHt1lTVa_-OWo9xlmCJoC0PO8w&amp;oe=69CA2612</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-09T15:36:07+0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18061546706320262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔥 Saiu do forno: últimas palestras do BBDW estão disponíveis!
-A 4ª edição do BB Digital Week movimentou Brasília em 2025 com mais de 500 conteudistas e 280 painéis – e agora você pode rever tudo no YouTube do ComunicaTI BB.
-Sabe aquela palestra que marcou?  Já pode dar o play* 🎥✨
-Tem conteúdo sobre Drex, CX, Design, Open Finance, IA, futuro do trabalho e muito mais. 
-Destaques que já estão liberados:
-▫️Agile no Spotify, com Luiz Carrari
-▫️Modernização com IA, com Bruno Borges (Microsoft)
-▫️Carreira do designer na era da IA, com Rodrigo Lemes (Mercado Livre)
-▫️Oracle IA e GenAI, com Luciano de Pinho
-▫️Team Topologies, com Manuel Pais
-*Keynotes não estão disponíveis
-🚀💛 O BBDW segue mostrando a força da Tecnologia BB e como estamos impulsionando a inovação no país. 
-👉 Bora assistir?
-Acesse as playlists atualizadas em: YouTube.com/ComunicaTIBB
-#Tecnologia #TI #vidadedev #inovaçao 
-#Pratodosverem Vídeo mostra imagens de palestrantes e palcos do BBDW. Surgem as frases: Confira as palestras do terceiro dia de bbdw e relembre os melhores momentos. Acesse as playlists no nosso canal, icone do youtube, texto ComunicaTI BB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://scontent-ord5-3.cdninstagram.com/o1/v/t2/f2/m86/AQN4TvKqqLJDg9aZ7vHEb7iLslHjnRCuf85fgoK0JnWgL6RRMeICnY34W4nJRSG_8QA_9UEQnO2Ilt107GEpPGlKgcwXQ4wjkP-dvvc.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;_nc_ohc=IHQ-smKme2oQ7kNvwFXzm6M&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNjA4LmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzI0Mjk4MjgzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo0NywidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjIxLCJ3YXRjaF90aW1lX3MiOjUzNiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=3b566e42c89539ef&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8yMjRCQkI2QTA0QzM0QkIxOTMxRUNFNEZFNjNDRDBCNl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlGNDE3NzJBRDgxQTgxNzcxODQ3MjQwQzlDQ0I0Nzg5X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW8oOK0e7HQBUCKAJDMywXQDV3S8an754YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=bAyYPRwHEm9TES00M56iVA&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfzH3fxx3uXZz5u73uLeFu3fCuiTNU6HPoIIPySbV66kmA&amp;oe=69C61668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-06T01:07:07+0000</t>
   </si>
 </sst>
 </file>
@@ -937,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -951,16 +953,16 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -968,13 +970,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
@@ -983,10 +985,10 @@
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1006,10 +1008,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1020,7 +1022,7 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -1029,10 +1031,10 @@
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1045,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -1052,10 +1054,10 @@
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1066,7 +1068,7 @@
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -1075,10 +1077,10 @@
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1098,10 +1100,10 @@
         <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1112,7 +1114,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -1121,10 +1123,10 @@
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1135,7 +1137,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
@@ -1144,10 +1146,10 @@
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1158,7 +1160,7 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
@@ -1167,7 +1169,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1190,7 +1192,7 @@
         <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1204,7 +1206,7 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
         <v>60</v>
@@ -1213,10 +1215,10 @@
         <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1236,10 +1238,10 @@
         <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1259,7 +1261,7 @@
         <v>69</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1273,7 +1275,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -1282,10 +1284,10 @@
         <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>325</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1296,7 +1298,7 @@
         <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>76</v>
@@ -1305,10 +1307,10 @@
         <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -1319,7 +1321,7 @@
         <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
@@ -1328,7 +1330,7 @@
         <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1342,7 +1344,7 @@
         <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
         <v>84</v>
@@ -1351,10 +1353,10 @@
         <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1374,10 +1376,10 @@
         <v>89</v>
       </c>
       <c r="F21" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1388,7 +1390,7 @@
         <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
         <v>92</v>
@@ -1397,10 +1399,10 @@
         <v>93</v>
       </c>
       <c r="F22" t="n">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1411,7 +1413,7 @@
         <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
         <v>96</v>
@@ -1420,10 +1422,10 @@
         <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1434,7 +1436,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -1443,10 +1445,10 @@
         <v>101</v>
       </c>
       <c r="F24" t="n">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1466,10 +1468,10 @@
         <v>105</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1480,7 +1482,7 @@
         <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
         <v>108</v>
@@ -1489,10 +1491,10 @@
         <v>109</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/instagram_posts.xlsx
+++ b/instagram_posts.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">IMAGE</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dN1gHICDS0oQ7kNvwHgD4Zy&amp;_nc_oc=Ado6iKjfwhMgvs4erd9wbyiNXpJ_NN79GOjITXZUfkybBsxrvnxKKQryJgMUBJ4QxwA&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afxr_yaGHZLcIhsdpcS59iS4EQYwiyAdkzwCwqtQe75qHg&amp;oe=69CA2BA6</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dN1gHICDS0oQ7kNvwFeNGdp&amp;_nc_oc=AdrLsrj-4ulEp1iaZRb6P_iPYEeEkvlBnjKjEWjOtne_B0TUW0wYFb_IVdo8km79Tjg&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxkJs17q3iuv9ZkyO0yRjpELdHDO6DIUuweQPCGQLK_8A&amp;oe=69CA2BA6</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T21:00:00+0000</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">CAROUSEL_ALBUM</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwEySDv2&amp;_nc_oc=AdqbuAFsVfFvJKgKDdu0XFl9PZbGd6yWQnrXpnMz66iSY4lfxcR0RQ4hgFhELyGAHLk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxzOu7O4AQDNhNemh9tj6xnNdt_xT13dXYkakxLPpHnPg&amp;oe=69CA2E1B</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwFyxMrg&amp;_nc_oc=Adp2BMjPsOlZmGNFRJURCPScGVS2V8L2tFtRtH62qmCbDPTfjmFuTUmCaqp96mP5uC4&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfyOSm6pWFWy_YwYDA_-37ezNL1o6NlYGDa4BwjRC9ZCPQ&amp;oe=69CA2E1B</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T13:59:41+0000</t>
@@ -102,7 +102,7 @@
 #IA #SegurançaDigital #Cibersegurança #Inovação #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwE4w0XM&amp;_nc_oc=Adp8pLPVNcr0CkJ1PWbuTwJSubkKxkBWmxfPqQAxpk59GIv3CqmKOx0eRP1TgnBnmck&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxMYuUiPIEwnG6kVXQvYiH2oMb2iSRBpLccINCpLc6tIw&amp;oe=69CA0F9A</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwGHHi04&amp;_nc_oc=AdrXVb6EW6WMMGA0XeEmPUsbAuvuyAxTrX0tleRn8TUGZjgziLHXt0WQUQ_imxWBPHE&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfwhA9xLS3HCTubCL644zr84aVO8xtP8SrBRXdv7yg1-9w&amp;oe=69CA47DA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T21:00:00+0000</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">VIDEO</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwGkukJS&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoyLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfwmDil3QERwZrVhUfNHKlzAtomLy0fehyEudywAUf9AhA&amp;oe=69CA3274</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwEuLLMU&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoyLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afx4GKkEo-WqcOAJB1YdmgxdGMGU54E57fbZ_in8cm5-RA&amp;oe=69CA3274</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T13:52:41+0000</t>
@@ -151,7 +151,7 @@
 #comunicatibb #Cibersegurança #SegurançaDigital #Tecnologia #DicasDeTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwFnMtK4&amp;_nc_oc=AdrcahQc30cHYACaxVJB3--ads6UU4ksFscbZD151Xhhx7WkiY1zAr31I8Zg1bLMSzk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzOJPPi8WlGizVjNCDI_GoCgZH2u9aNgwBQRpMBVzcamw&amp;oe=69CA16FC</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwGgjBvw&amp;_nc_oc=Adp_K_4RuL38GmZ7pLiEdWPuXePtCPIbyDNCjN8jssuAowXBwTUD2ceqjgAX38mfFKo&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfypyKpH0uzlFj6n0fORtNZlgoNlzlJzprIwAVCKNB6yQg&amp;oe=69CA16FC</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T21:00:00+0000</t>
@@ -170,7 +170,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwGVQt1J&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo1LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afz7o_OM8qiApjyYudO74inVroBgXeYwDhOy_VoD9_4WNA&amp;oe=69CA1147</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwEzYUXX&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo1LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afw8UPa3VX3Clx7m4K5Awq0eTPuPae7JoW2DINCn64TNgw&amp;oe=69CA1147</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T12:33:26+0000</t>
@@ -187,7 +187,7 @@
 #RacismoAlgoritmico #InteligenciaArtificial #Diversidade #TecnologiaEtica #InclusãoDigital</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwFaoIQ4&amp;_nc_oc=AdpqzmRFOD5U1Ilveh5aSq6UUwdsCqONGuXedraqYf0dq-nclwsCGAFdU6tEmRxCaIw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxJTukKs31ihSur4Mq0Hzr3zduHBbeEydjhZ41ZJdP5kQ&amp;oe=69CA3A04</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwGohwMY&amp;_nc_oc=AdpbugjxrFoxsJ1D2XNRHUdZ68GJqsydAfclIeeZWFdbYEJ1EKSRqNTF-JJhRyIFQxs&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx423qO0aZSHe-kNEeIsMMqxq3wxjTIhIvciqm6XaCDSA&amp;oe=69CA3A04</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-18T16:51:12+0000</t>
@@ -206,7 +206,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwHIZ_88&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfwaQsllX2eOTp9h5pq3RisyYcQCMSj-nhxgDteASScNVQ&amp;oe=69CA353F</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwHriDhL&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afx7E6jJBEzCg4o8DG0olpkiC838pGBLAPqdNxrRvTsmWQ&amp;oe=69CA353F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T21:00:00+0000</t>
@@ -231,7 +231,7 @@
 #Meta #InteligênciaArtificial #Tecnologia #Inovação #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwE6PYr5&amp;_nc_oc=AdoReFxSOTP8OZpaslIfuouUZDe8Dzx0J8WHfW_jL_VAVmBkCfy2NPub8_KTfgrcrkE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfwZEzLQsr7s2UJpuns6vKwNRAQXf4IHPdzPoYyzjLzHBg&amp;oe=69CA0B11</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwHP_dCU&amp;_nc_oc=Adrb64O_cGfonG5Rjji2R9lUYGJML6AI110wYo4q1tXxMlWzk2D7b9yQTnmqDvqkJvs&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afy3VQcUVq16vvnlP0m35y5Jd2HleqbGGm-7L54WM2waLA&amp;oe=69CA4351</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T16:36:23+0000</t>
@@ -247,7 +247,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFqNaMb&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfykJgFimn3vB5_X5k3xLf4Wf1XnfPNayIHklOK9UV2aTA&amp;oe=69CA40B9</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFHkUWY&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxkeD6Dsz1wXS8Jfxs1x_Nc9ivy5iCK1eGSeSqShFCZzw&amp;oe=69CA40B9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T21:00:00+0000</t>
@@ -263,7 +263,7 @@
 #ECADigital #DesenvolvimentoDeSoftware #PrivacidadeDeDados #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwG1p8Uv&amp;_nc_oc=Adrgd9iU47lN1un1oXXzzp0SBKx4s0XV8uDkyNB__wWPrrBdpXmoRKBD4fL-msoHW98&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfwNO_4SY0uwBMaAMBz9mDKIb_s9tcIjGzSycu00OM8xHw&amp;oe=69CA2BF9</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwFP4UYf&amp;_nc_oc=AdpY7ub697BVW-_oBzk-HeYRb7KXxgRdnMFCTT9kF15z3wo4KT15Vp31FTd8P_rfft0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxKVMYXBgyAkhYDzn-Mf-7FN-rlYQ-S0ZxP0_iqX3tCQw&amp;oe=69CA2BF9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T16:30:40+0000</t>
@@ -282,7 +282,7 @@
 #Tecnologia #IA #Hardware #SupplyChain Inovaç</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=agFoXPhlYxwQ7kNvwHHFZlB&amp;_nc_oc=AdoIcubrFfcA_vfhr3m_mxkcTbKdm1Zs_xAsNEicrb167vBAOV4rNKYIsjMytQZQUxA&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfwUlYqoT1mFx9San02eMHMgQS5xrIKkFGGYDo9_sAYMkA&amp;oe=69CA28F7</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=agFoXPhlYxwQ7kNvwF1JXlq&amp;_nc_oc=AdoRGidn6VqITp6k5aHEyMiLqGGGPkmh5Xh7vr51sSs9p41OWah_ZzPoIusJ8h_RPoQ&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfzfTeD_r8CEvXjzuoy022NWQ-s90hVghMak1JbzXTnuqg&amp;oe=69CA28F7</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-12T15:04:46+0000</t>
@@ -299,7 +299,7 @@
 #Cibersegurança #ComunicatIBB #ProteçãoDeDados #SegurançaDigital #SegurançaFinanceira</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwG2VIKj&amp;_nc_oc=AdpPWfTCnQLMqnuAAlFBbyqNtHulhWAR7abqMabV4jCkL2VPNcsVwGbzerwcpiovSXI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzLOmPx3P3prmZfAdytpldHq7aD7pmpS5dSgjX3haUpLw&amp;oe=69CA1FE8</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwHGB-AR&amp;_nc_oc=AdqZJz83Dt_q45Z5toVYhsk3ghOFVYxqhjb3dAYBZoQyHy2aa6m3dk1e42oPwAKJ8P8&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfwyM0XUkAOukMos4p-0hD816vRYecGTsQmWr3uhjNotPw&amp;oe=69CA1FE8</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T21:00:00+0000</t>
@@ -318,7 +318,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwESi3nI&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfyQNvzhRWjuXRotKeZyT6pRasy3olaF4reoi4AxO6fkew&amp;oe=69CA195E</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwEfybbs&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afy9NhudmySm1qK2S82sUiRypoNB6Mv8e3yC2TpZMgOIaQ&amp;oe=69CA195E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T13:48:44+0000</t>
@@ -336,7 +336,7 @@
 #ColunistasBB #ComunicaTI #CompartilheConhecimento</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwHd1rUc&amp;_nc_oc=AdrTJaYPclVj0f4ZMooWMdA_px6Ph5HcN6lrxTkGuk6_-trfAdkoCtjfrtMYvLj9dpE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzKup0U34L-RxLW1YVguu4NhKqzbPqBEJUI5pRS0HwfDA&amp;oe=69CA3F48</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwH3Xbg0&amp;_nc_oc=Adox6UAl9-z79bJ8K58y79qhL6_NAOrm4I-JTUXzGxeEiT_-BAmbF37mdXr_S1eDdos&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfyCYv5ROUi5emHXmz0NZjdS6SZVmX9ZHdqO4yuLDFM_Rg&amp;oe=69CA3F48</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-10T17:21:57+0000</t>
@@ -361,7 +361,7 @@
 #GuildasBB #TecnologiaBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwETz-kf&amp;_nc_oc=Ado6HPVYYcZ9-0ZGGzMqv0wkIQfPwPIK1whrt5Xz385pPKQR7-0e4V_wZc_khDkj2jI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afx92_jZ8FeUwM8myJHs4kJEHuokb5Wb9heuyrTEwSGlHg&amp;oe=69CA17AE</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwH5zNwe&amp;_nc_oc=Adrij3WJ-ilqkumTiSAfrKQbtteDqYQhjuoiZ1FFd_FpsV2sF9lHLe_n5rqZW6d-U7M&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxSpKTLhWZtl3dIfzsS7JxrVRHLnVLMY9YHUKFNnAkunw&amp;oe=69CA17AE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-09T13:59:40+0000</t>
@@ -378,7 +378,7 @@
 Feliz Dia Internacional das Mulheres. 💙💛</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwGJt03Q&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afy6HzcSsbNLVCWpuhYwkOTDervtapcT2LYNtWKPqODJrg&amp;oe=69CA0D44</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwEl5ER9&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afyg6yXZvrg8KuCkuEKQIhwBQfEIp5zGjP19BknhWaTL_Q&amp;oe=69CA4584</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-06T20:47:29+0000</t>
@@ -395,7 +395,7 @@
 #InteligenciaArtificial #Sustentabilidade #Tecnologia #IAVerde #Inovacao ComunicaTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwH5r7UV&amp;_nc_oc=AdqVClhmC4cqtgxSL3XUPtIDyABUb6CMOTUn7OLOSkpjUJYsCy7w7AgIJqlTTUhGbmE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfyAiaF6DAo_faFM8WVUBVCIfp9x6Ess7ZdsqsStYvCUMQ&amp;oe=69CA2B5F</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwG0guWl&amp;_nc_oc=Adqje3k1qeKI5SbAlajSu2-kleLs-cqDroiLbv8fnHz8FohUDBOp8-CKtbJ6y8S04Nk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxkAfXCGkzHYprUgZVRmnjzSQqMs3UnPLVtdIBeiuwvzA&amp;oe=69CA2B5F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-04T17:32:16+0000</t>
@@ -430,7 +430,7 @@
 Salve na agenda e participe! 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwGksi6C&amp;_nc_oc=Adr8iF8K6PgLLMS83XrdIHcupDmSND_8CKQy3JTuUJe8cyMh6RjzwR-ylfw07ONOT7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxkUXivKFqw5cGovPyMghLMH-gclv3CVOMgU5Di66u4Eg&amp;oe=69CA11AE</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwHVAYtT&amp;_nc_oc=AdoKya3lSDO6XGyZwfuhpdnbfOJZ91RW7rbDt7k-rjcucHanlLmNZnsvSwyg54Uj7YQ&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfyAERqUvtDM9Fge_DbdZxg_ltqpV7lBJ3E90kSncrbtdQ&amp;oe=69CA11AE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T18:48:00+0000</t>
@@ -457,7 +457,7 @@
 #MulheresNaTI #Carreira #LiderançaFeminina #Mentoria</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwGE_8qi&amp;_nc_oc=Adql3TaeguCmttovc5MDkQGohXdx6IX-FFsep97wIZ9TN7rR_81HfofU0cSuF3p4LmU&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzbxhbiFW2UQM4W96irevhTTwD6IYJ_kE1D0cAMvlwRFw&amp;oe=69CA11CA</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwGV3ncO&amp;_nc_oc=AdrTIHyalBEsn8M4wILDsVwd5cNUGWFP9nrdCzL6pZU-IP1zfxjBUZrL0dPlmOEEcN0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx5OrhQTYZE44jG5e1qeZd2I5iKTSdKEwz0g-4gVbivgw&amp;oe=69CA11CA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T16:15:52+0000</t>
@@ -471,7 +471,7 @@
 #ComunicaTI #Ditec #BancoDoBrasil #SomosBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwGzsXwP&amp;_nc_oc=Adqqfkn33TpL7QVDMVLey0EZjgBvpd2OeMWMANuCdz4CRFpmqw6fmSDNVK8McWe0dJw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfxL6VnbZWkzAqwFVyzrj18QjEOcD4jc26qiD3MdhFoaSQ&amp;oe=69CA26E6</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwG34GEo&amp;_nc_oc=AdpMcEjqlqibrxRPCXg7EwG06bMgIQ_7bHilEQaQ-X_slYpAVJqQb1N2-UJhViz_yW8&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx5msgEXR6RnjNuu4YtxICQILJUqgyc4xu472Hz9eucrg&amp;oe=69CA26E6</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-25T17:10:36+0000</t>
@@ -495,7 +495,7 @@
 #BankingTransformation #Inovação #TecnologiaBB #bancodobrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-3.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwFEFEjo&amp;_nc_oc=Adq0reI_EcDevWGiQ41IEnrvQ0O96Z5KxpCtuoZ_6wmTeO5mgsEinRv2UWvRpMKRfhU&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afyt_Pm8yL17rxZj2HtX2m8Lm_gsZVRYFKrb-TBGahTsxA&amp;oe=69CA19B5</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwHRzknA&amp;_nc_oc=Adom-cfCLiDZEqfdqXt3V-GqIMmhWzgFmFr3O26O9c-BOE83lK8Z2bOfi9C2n6B6akM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afwk6m7FMsRu02nEP3JP9hwGkNNSfMuM0cZZHs4Lw5QAJw&amp;oe=69CA19B5</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-24T00:45:36+0000</t>
@@ -527,7 +527,7 @@
 #GuildasDaSemana #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwE0URcI&amp;_nc_oc=AdoLb3gFatZ-dA_zenAJgUPLUZAzahnHJMaaVfY-eywkddlBb-3stmVxcsByJbMbCOI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfyWZkeE2e9kxCXJ_vBTh6XhOfCCrKz9iKu5VOIVYCIZZQ&amp;oe=69CA355E</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwH8fXPU&amp;_nc_oc=Adp_rZm-GR8GAfQTjXy0bBZ73QsGLDfSS3z5Iv5-ccIH4cKkzosVSLo6fMXMdk71FnA&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx8fRIrNsVTMVvCMfqW4_PNOnV5lXU-aLuXBi_NA2Q2Hw&amp;oe=69CA355E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-23T12:27:17+0000</t>
@@ -545,7 +545,7 @@
 #MeninasNaCiência #MulheresNaCiência #MeninasNaCiência #WomenInScience #Inovação</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwFtOV0v&amp;_nc_oc=AdqckHdbaSEVMKErx4dUWvoBN2SrSw5nW3lYwqbw3IeovRY47uc30pdgmgJLKdSltVw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_Afx1eK6YfIDiFzK6G02xhfyqS4gztxB8knMnSl_DVSVR4w&amp;oe=69CA3C8F</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwHOEMFd&amp;_nc_oc=AdoY2cAe6NLR2WesCgcIA3KLRtSO2Ld7hgtqdVavwiRvApn1x-wvgyYmJbmH_KXUbAk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afyt8X7eXCjgTAQg2RgUA-fcu66NcLCIhizBAd_3NYEKnw&amp;oe=69CA3C8F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-11T13:46:50+0000</t>
@@ -567,7 +567,7 @@
 #GuildasDaSemana #Tecnologia #TI #Dados DividaTecnica Analytics IA BancoDoBrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwEn9AX1&amp;_nc_oc=AdpAcjJf7lXngd2dbxfjiZMR2rnQBZBXD-C88xxyIfC4B4GMUBYJUwV5Llw7CgGwymI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=UWvqUzCmqbbd82HuGnIvpg&amp;oh=00_AfzJ9_OyPdQYKvxbNwAMvHt1lTVa_-OWo9xlmCJoC0PO8w&amp;oe=69CA2612</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwHOxSr6&amp;_nc_oc=Adqf3Wlkmd_gCjlHZ-OPDU6JcfoC60d5KNlhLz7fvz8k1jJh5k1UM7bkYhz7z4p5wBY&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfwM8n28woZgNByU56AshjY1oI0y5vUOS5UEsMpVaqCsaw&amp;oe=69CA2612</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-09T15:36:07+0000</t>

--- a/instagram_posts.xlsx
+++ b/instagram_posts.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">IMAGE</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dN1gHICDS0oQ7kNvwFeNGdp&amp;_nc_oc=AdrLsrj-4ulEp1iaZRb6P_iPYEeEkvlBnjKjEWjOtne_B0TUW0wYFb_IVdo8km79Tjg&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxkJs17q3iuv9ZkyO0yRjpELdHDO6DIUuweQPCGQLK_8A&amp;oe=69CA2BA6</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=aLqu5e6IrgQQ7kNvwFxN4KV&amp;_nc_oc=AdqskFOeLdBa-WtsqyDvOsfY9HZfcTk4RIlenLVvguqDdpQLVp9KbVjQcSIZ3Sl4DCo&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afyyl__pWmoTNHbnWYnggG90Go2sNk_VO88C8g6tQoAgpA&amp;oe=69CB0CA6</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T21:00:00+0000</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">CAROUSEL_ALBUM</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwFyxMrg&amp;_nc_oc=Adp2BMjPsOlZmGNFRJURCPScGVS2V8L2tFtRtH62qmCbDPTfjmFuTUmCaqp96mP5uC4&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfyOSm6pWFWy_YwYDA_-37ezNL1o6NlYGDa4BwjRC9ZCPQ&amp;oe=69CA2E1B</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwECZH4U&amp;_nc_oc=AdrgnC9h3Hp5f6FEYJnyBEhk8LQYAnQChtV9BYkaZG9lM_uk8oo7QsXaMO1mIr1wStA&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afy2BkGfZszlirffzdpqHFvDib59GnOFdrsP8vyEd7nTZA&amp;oe=69CB0F1B</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T13:59:41+0000</t>
@@ -102,7 +102,7 @@
 #IA #SegurançaDigital #Cibersegurança #Inovação #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwGHHi04&amp;_nc_oc=AdrXVb6EW6WMMGA0XeEmPUsbAuvuyAxTrX0tleRn8TUGZjgziLHXt0WQUQ_imxWBPHE&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfwhA9xLS3HCTubCL644zr84aVO8xtP8SrBRXdv7yg1-9w&amp;oe=69CA47DA</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwFk43EU&amp;_nc_oc=Adrm5FogvzTWOfHwfy95Ka72l4a2kKdkj86OtGwHnPRf_ROrG-zC0kE1fTZ-bynihNE&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwHjDd-LHT_Wkp5SavXxKxEajnk0UTrRXQv2e9Vt312jg&amp;oe=69CB28DA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T21:00:00+0000</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">VIDEO</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwEuLLMU&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoyLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afx4GKkEo-WqcOAJB1YdmgxdGMGU54E57fbZ_in8cm5-RA&amp;oe=69CA3274</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwE5h5ET&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjozLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afzq7094vK6klOEfc-95JVTLgc8oT8o_ShtEPoskNya6KQ&amp;oe=69CB1374</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T13:52:41+0000</t>
@@ -151,7 +151,7 @@
 #comunicatibb #Cibersegurança #SegurançaDigital #Tecnologia #DicasDeTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwGgjBvw&amp;_nc_oc=Adp_K_4RuL38GmZ7pLiEdWPuXePtCPIbyDNCjN8jssuAowXBwTUD2ceqjgAX38mfFKo&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfypyKpH0uzlFj6n0fORtNZlgoNlzlJzprIwAVCKNB6yQg&amp;oe=69CA16FC</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwGspcu6&amp;_nc_oc=Adrgu3uaQrJ_Dkq3i4ge8UpFGlzxUXAaXKrveLNM-TYt3U3Ec5U8-dFYlsQwd2RwHAM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afxo11BtsOe74CqiFeb7-Jk73U8EtRKZnWooWZqiveKJSw&amp;oe=69CAF7FC</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T21:00:00+0000</t>
@@ -170,7 +170,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwEzYUXX&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo1LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afw8UPa3VX3Clx7m4K5Awq0eTPuPae7JoW2DINCn64TNgw&amp;oe=69CA1147</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwHhsUrK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo2LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxJD7hvxVzxFfpO1z4MUDCiKr1LMSGjk-sqbySwBRdCFQ&amp;oe=69CAF247</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T12:33:26+0000</t>
@@ -187,7 +187,7 @@
 #RacismoAlgoritmico #InteligenciaArtificial #Diversidade #TecnologiaEtica #InclusãoDigital</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwGohwMY&amp;_nc_oc=AdpbugjxrFoxsJ1D2XNRHUdZ68GJqsydAfclIeeZWFdbYEJ1EKSRqNTF-JJhRyIFQxs&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx423qO0aZSHe-kNEeIsMMqxq3wxjTIhIvciqm6XaCDSA&amp;oe=69CA3A04</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwEJPwXv&amp;_nc_oc=Adr8Bkbcj0W6hN0GJMl9Vr0sZtSNH-sz_B1u8znZbJePxTKD2-2rnTRZbBLsph3LDW0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afzow0E3L3dwI-HncXWPn9UX0PJR76d--BuW2dJIOc04yw&amp;oe=69CB1B04</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-18T16:51:12+0000</t>
@@ -206,7 +206,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwHriDhL&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afx7E6jJBEzCg4o8DG0olpkiC838pGBLAPqdNxrRvTsmWQ&amp;oe=69CA353F</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwE2Jx3D&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxBNhbftIlN8XNGbnwsnvPfA_CBqfw9rN0MyjPHx4eNMg&amp;oe=69CB163F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T21:00:00+0000</t>
@@ -231,7 +231,7 @@
 #Meta #InteligênciaArtificial #Tecnologia #Inovação #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwHP_dCU&amp;_nc_oc=Adrb64O_cGfonG5Rjji2R9lUYGJML6AI110wYo4q1tXxMlWzk2D7b9yQTnmqDvqkJvs&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afy3VQcUVq16vvnlP0m35y5Jd2HleqbGGm-7L54WM2waLA&amp;oe=69CA4351</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwF6-6wZ&amp;_nc_oc=AdorHO76N-ZhyrGugR6DajxZeGVtiJk5uBBg98R20stgSbaaKepIxwbQn8ngiEAyHBc&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afywufrgv3V4UBbU2D121TRjOPMY-uJsCD-J1H5XhVvpVA&amp;oe=69CB2451</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T16:36:23+0000</t>
@@ -247,7 +247,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFHkUWY&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxkeD6Dsz1wXS8Jfxs1x_Nc9ivy5iCK1eGSeSqShFCZzw&amp;oe=69CA40B9</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFCXR5k&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afwk-H14Dk-yde7XLUxFVsrUU_ymQ8pBkjuYJzrmVgwjhg&amp;oe=69CB21B9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T21:00:00+0000</t>
@@ -263,7 +263,7 @@
 #ECADigital #DesenvolvimentoDeSoftware #PrivacidadeDeDados #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwFP4UYf&amp;_nc_oc=AdpY7ub697BVW-_oBzk-HeYRb7KXxgRdnMFCTT9kF15z3wo4KT15Vp31FTd8P_rfft0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxKVMYXBgyAkhYDzn-Mf-7FN-rlYQ-S0ZxP0_iqX3tCQw&amp;oe=69CA2BF9</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwGTGWqY&amp;_nc_oc=AdqZ4fAWuV87a8CdWPeAnV3MO-Nezz53wdIiQC0icZ3OLYq-_0nwclAWH_WvB6ssrY8&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfyKtzs1a41DiZWVWpopaDAPJMh-fgmhxNRjoknsFtBihg&amp;oe=69CB0CF9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T16:30:40+0000</t>
@@ -282,7 +282,7 @@
 #Tecnologia #IA #Hardware #SupplyChain Inovaç</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=agFoXPhlYxwQ7kNvwF1JXlq&amp;_nc_oc=AdoRGidn6VqITp6k5aHEyMiLqGGGPkmh5Xh7vr51sSs9p41OWah_ZzPoIusJ8h_RPoQ&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfzfTeD_r8CEvXjzuoy022NWQ-s90hVghMak1JbzXTnuqg&amp;oe=69CA28F7</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=2qJBgyE8haYQ7kNvwFY36Hh&amp;_nc_oc=AdrpmDAeHZpMqE6-Qpk4QoH5Ol4Hm-niZG5flr9mRhsZSkpDYAnjMXrbQWKeEIMNMUc&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afw7OBZOScnhPFG_64UMsAuXIPItYTuhfl6FDFh4mwnHmA&amp;oe=69CB09F7</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-12T15:04:46+0000</t>
@@ -299,7 +299,7 @@
 #Cibersegurança #ComunicatIBB #ProteçãoDeDados #SegurançaDigital #SegurançaFinanceira</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwHGB-AR&amp;_nc_oc=AdqZJz83Dt_q45Z5toVYhsk3ghOFVYxqhjb3dAYBZoQyHy2aa6m3dk1e42oPwAKJ8P8&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfwyM0XUkAOukMos4p-0hD816vRYecGTsQmWr3uhjNotPw&amp;oe=69CA1FE8</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwEz1St9&amp;_nc_oc=AdqF9ZrlprWTkbazM94yho3fbDQ5yDg3s3ycB7yhexDFNhI6CAYVap0OwuKJHMR58Ac&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfzWc-2xhTDIcsGPKBF_TADTD7nJQL4jnFf5ElXDNyPWrQ&amp;oe=69CB00E8</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T21:00:00+0000</t>
@@ -318,7 +318,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwEfybbs&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNCwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afy9NhudmySm1qK2S82sUiRypoNB6Mv8e3yC2TpZMgOIaQ&amp;oe=69CA195E</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwGm9BXf&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afxb-F8uUFsiRs9KbabJl62q4bq9Gllu9k1k6JFPPclARw&amp;oe=69CAFA5E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T13:48:44+0000</t>
@@ -336,7 +336,7 @@
 #ColunistasBB #ComunicaTI #CompartilheConhecimento</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwH3Xbg0&amp;_nc_oc=Adox6UAl9-z79bJ8K58y79qhL6_NAOrm4I-JTUXzGxeEiT_-BAmbF37mdXr_S1eDdos&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfyCYv5ROUi5emHXmz0NZjdS6SZVmX9ZHdqO4yuLDFM_Rg&amp;oe=69CA3F48</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwEMr2X6&amp;_nc_oc=Adod9Flz7NH0iKPFoJPJpEaut5e7RU8IGkJ30rInj85cEmmGRV8EtoUS8WESHwG2b_I&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afy-cNXVs54NqET45SUtqXp4StVC4uCJwYQGTPyMv8KyuQ&amp;oe=69CB2048</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-10T17:21:57+0000</t>
@@ -361,7 +361,7 @@
 #GuildasBB #TecnologiaBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwH5zNwe&amp;_nc_oc=Adrij3WJ-ilqkumTiSAfrKQbtteDqYQhjuoiZ1FFd_FpsV2sF9lHLe_n5rqZW6d-U7M&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxSpKTLhWZtl3dIfzsS7JxrVRHLnVLMY9YHUKFNnAkunw&amp;oe=69CA17AE</t>
+    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwFR4bAF&amp;_nc_oc=AdqsxrS-pxXltBL1v8tH_T99n2nG0jlNDxOdgqTQaEnS4CL-ARAzpOAfmdUIHKzQbaM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afx5N5w5WsFXGj3cnbc0Eswl_5WTbduEXGdp8R6JxWSqUQ&amp;oe=69CAF8AE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-09T13:59:40+0000</t>
@@ -378,7 +378,7 @@
 Feliz Dia Internacional das Mulheres. 💙💛</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwEl5ER9&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afyg6yXZvrg8KuCkuEKQIhwBQfEIp5zGjP19BknhWaTL_Q&amp;oe=69CA4584</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwGq76mc&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afxr-0js-8fLvzwIcIaETJqU-ih97wPIG7DZyNry2-scXg&amp;oe=69CB2684</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-06T20:47:29+0000</t>
@@ -395,7 +395,7 @@
 #InteligenciaArtificial #Sustentabilidade #Tecnologia #IAVerde #Inovacao ComunicaTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwG0guWl&amp;_nc_oc=Adqje3k1qeKI5SbAlajSu2-kleLs-cqDroiLbv8fnHz8FohUDBOp8-CKtbJ6y8S04Nk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfxkAfXCGkzHYprUgZVRmnjzSQqMs3UnPLVtdIBeiuwvzA&amp;oe=69CA2B5F</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwG-jFz1&amp;_nc_oc=Adone5H7vvQ3bOB5OLytlaF8pAjb8MCUVLghGiZj1YGJM1je4LItBM-iGWBW9AP0lks&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfxHACEiEuM-nnUcoNECFRh_2PR6p67EYrBMOYyXC7awlw&amp;oe=69CB0C5F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-04T17:32:16+0000</t>
@@ -430,7 +430,7 @@
 Salve na agenda e participe! 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwHVAYtT&amp;_nc_oc=AdoKya3lSDO6XGyZwfuhpdnbfOJZ91RW7rbDt7k-rjcucHanlLmNZnsvSwyg54Uj7YQ&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfyAERqUvtDM9Fge_DbdZxg_ltqpV7lBJ3E90kSncrbtdQ&amp;oe=69CA11AE</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwFJygVk&amp;_nc_oc=AdrTrYtnspIxAa8m4d9DNfeQz53JXUanNBpT9w4G_Bp8wNUmC9EOZXWM2ZnSQJCaoUU&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwMZatKY0DaLGRiP44zTNA4Gad-iqoupTXUawdMbdLnaQ&amp;oe=69CAF2AE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T18:48:00+0000</t>
@@ -457,7 +457,7 @@
 #MulheresNaTI #Carreira #LiderançaFeminina #Mentoria</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwGV3ncO&amp;_nc_oc=AdrTIHyalBEsn8M4wILDsVwd5cNUGWFP9nrdCzL6pZU-IP1zfxjBUZrL0dPlmOEEcN0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx5OrhQTYZE44jG5e1qeZd2I5iKTSdKEwz0g-4gVbivgw&amp;oe=69CA11CA</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwHm8VsV&amp;_nc_oc=Ado_OTnyavDtblpS_-u9-bmm5d2EjXhRL9UoJ6ftxnZfHkvYmOJQeGpii1cF5vD8r9g&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfztZ82jMlGn_L--0eWzT8zJnpc9tmIRcNlxTollBBGz1w&amp;oe=69CAF2CA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T16:15:52+0000</t>
@@ -471,7 +471,7 @@
 #ComunicaTI #Ditec #BancoDoBrasil #SomosBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwG34GEo&amp;_nc_oc=AdpMcEjqlqibrxRPCXg7EwG06bMgIQ_7bHilEQaQ-X_slYpAVJqQb1N2-UJhViz_yW8&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx5msgEXR6RnjNuu4YtxICQILJUqgyc4xu472Hz9eucrg&amp;oe=69CA26E6</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwGKHINr&amp;_nc_oc=AdqUO9j7c4OHp2Y2-Ri9nvlFvVRmb_g91-SFFg458Hg02JtqgACb3HUi2Kf4jIROkrM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwLRcM1e83aWz8RuZkfa9wwlRcfWCauajASv6WuwhzTEw&amp;oe=69CB07E6</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-25T17:10:36+0000</t>
@@ -495,7 +495,7 @@
 #BankingTransformation #Inovação #TecnologiaBB #bancodobrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwHRzknA&amp;_nc_oc=Adom-cfCLiDZEqfdqXt3V-GqIMmhWzgFmFr3O26O9c-BOE83lK8Z2bOfi9C2n6B6akM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afwk6m7FMsRu02nEP3JP9hwGkNNSfMuM0cZZHs4Lw5QAJw&amp;oe=69CA19B5</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwF2khAw&amp;_nc_oc=Adr_c3l8Aub1MRQ-OkVlkc1EfMdUx26pYFxF4wP3RSWwZNeQhS2iKEsUlg3U00LT1Rg&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwBrknfAwDXF_GRSeOZtCnLur7jmbbz5Arm4lsEF829qQ&amp;oe=69CAFAB5</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-24T00:45:36+0000</t>
@@ -527,7 +527,7 @@
 #GuildasDaSemana #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwH8fXPU&amp;_nc_oc=Adp_rZm-GR8GAfQTjXy0bBZ73QsGLDfSS3z5Iv5-ccIH4cKkzosVSLo6fMXMdk71FnA&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afx8fRIrNsVTMVvCMfqW4_PNOnV5lXU-aLuXBi_NA2Q2Hw&amp;oe=69CA355E</t>
+    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwFxV0sw&amp;_nc_oc=AdoMS_J0_mrvMantjjnYqoSo12L7Vn4LxOq5D7uvdjyGvPnwDfA67RhmWqvvGKKdUMI&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfxZ65dRVAMr3tUYheTIg76zvGAG0pNFoQnRSUaNFLV7bQ&amp;oe=69CB165E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-23T12:27:17+0000</t>
@@ -545,7 +545,7 @@
 #MeninasNaCiência #MulheresNaCiência #MeninasNaCiência #WomenInScience #Inovação</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwHOEMFd&amp;_nc_oc=AdoY2cAe6NLR2WesCgcIA3KLRtSO2Ld7hgtqdVavwiRvApn1x-wvgyYmJbmH_KXUbAk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_Afyt8X7eXCjgTAQg2RgUA-fcu66NcLCIhizBAd_3NYEKnw&amp;oe=69CA3C8F</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwGPsul-&amp;_nc_oc=Adq2C2spjOtrtJjpKUaBn7Hhl-PAonwK7lPW6oWvdM-sQqigGdujVpbDoe_2u0WgLH0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwOihKVaZEF0oTotcHhIj7Ys2Quz2Fi6qJt-Th9efIBJQ&amp;oe=69CB1D8F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-11T13:46:50+0000</t>
@@ -567,7 +567,7 @@
 #GuildasDaSemana #Tecnologia #TI #Dados DividaTecnica Analytics IA BancoDoBrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwHOxSr6&amp;_nc_oc=Adqf3Wlkmd_gCjlHZ-OPDU6JcfoC60d5KNlhLz7fvz8k1jJh5k1UM7bkYhz7z4p5wBY&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=S0EYRvhCjv2OAi-0s51iLw&amp;oh=00_AfwM8n28woZgNByU56AshjY1oI0y5vUOS5UEsMpVaqCsaw&amp;oe=69CA2612</t>
+    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwF-YSqH&amp;_nc_oc=AdpGw4jb0E_cB4gxD_94K8p8cSpacCvezdCK0UHn3sA7mkgBYKyjvFiOKqbapU5c0kk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afxx_0dyjNjPfPEswaFifIs_DfSoYagofo7HirHLL05gXA&amp;oe=69CB0712</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-09T15:36:07+0000</t>
@@ -939,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>69</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1307,7 +1307,7 @@
         <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G18" t="n">
         <v>33</v>
@@ -1330,7 +1330,7 @@
         <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>

--- a/instagram_posts.xlsx
+++ b/instagram_posts.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">IMAGE</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=aLqu5e6IrgQQ7kNvwFxN4KV&amp;_nc_oc=AdqskFOeLdBa-WtsqyDvOsfY9HZfcTk4RIlenLVvguqDdpQLVp9KbVjQcSIZ3Sl4DCo&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afyyl__pWmoTNHbnWYnggG90Go2sNk_VO88C8g6tQoAgpA&amp;oe=69CB0CA6</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/658177071_18177800554390059_1764118133549304550_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=aLqu5e6IrgQQ7kNvwFSkLBs&amp;_nc_oc=Adp-GSg8sCQGahNOFPvDBLb_MvPnoCm619HJvffsjEy6vORIbnmtZX17PNkDL5ZCGPg&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afw9_HmT4mQNWVqu3rKOIVDihTprqpj4mMTiNpTHTE86vA&amp;oe=69CB0CA6</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T21:00:00+0000</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">CAROUSEL_ALBUM</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwECZH4U&amp;_nc_oc=AdrgnC9h3Hp5f6FEYJnyBEhk8LQYAnQChtV9BYkaZG9lM_uk8oo7QsXaMO1mIr1wStA&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afy2BkGfZszlirffzdpqHFvDib59GnOFdrsP8vyEd7nTZA&amp;oe=69CB0F1B</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/656755189_18177758743390059_7284614199813760554_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=q0zHndP1NoEQ7kNvwEOGsQ5&amp;_nc_oc=AdosRjK8u4HfZQIteBscXsfrPgLBvShHZ2xpTBdG4O70TGLi3q__hIqDQlwrFLaW_K4&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfxLvXM3AIIl3mY7ftqQSd8oqTEFCs5MtAJnh8Y7As9s8w&amp;oe=69CB0F1B</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-25T13:59:41+0000</t>
@@ -102,7 +102,7 @@
 #IA #SegurançaDigital #Cibersegurança #Inovação #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwFk43EU&amp;_nc_oc=Adrm5FogvzTWOfHwfy95Ka72l4a2kKdkj86OtGwHnPRf_ROrG-zC0kE1fTZ-bynihNE&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwHjDd-LHT_Wkp5SavXxKxEajnk0UTrRXQv2e9Vt312jg&amp;oe=69CB28DA</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/656279228_18177513127390059_7736238303520731783_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=-RdiekvlHRoQ7kNvwGDz-pS&amp;_nc_oc=AdqHS47JpXUOfut6NGclJUNmNAE6Kzi0DwsMHrsIGUezU17iHU_V-yYqBfeEB5JuIqE&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfzM76AtvYiO5PYXUtxUL3-G4J3-vUB06KVlB_cnSdelmg&amp;oe=69CB28DA</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T21:00:00+0000</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">VIDEO</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwE5h5ET&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjozLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afzq7094vK6klOEfc-95JVTLgc8oT8o_ShtEPoskNya6KQ&amp;oe=69CB1374</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/o1/v/t16/f2/m69/AQM3K_6c698fyiFi4NCc-cAo0NxdjMSILHJOvHdbmvNPqHKiWglTA7wyJ5p4sCBhkkt_hSvs8nIq0mhrGo2YQIN8.mp4?strext=1&amp;_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=OnjI6wcFJJoQ7kNvwGRzXbp&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzc0NTA0MjEzOTAwNTksImFzc2V0X2FnZV9kYXlzIjozLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTAzLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=dd2932555be24d84&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRHlkLWlhcURuX25OWmtFQU5SX0Z6U1ZZTllzYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA5NEQyOERERjFDQjc5NEJDQjJBMEFFMDJFOTU3MkJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWq9C075LKQBUCKAJDMywXQFntT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxF8RpkjFARtJV3vx2m0vJE1-ydkuHkoiF0c_mJWjP8hA&amp;oe=69CB1374</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-23T13:52:41+0000</t>
@@ -151,7 +151,7 @@
 #comunicatibb #Cibersegurança #SegurançaDigital #Tecnologia #DicasDeTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwGspcu6&amp;_nc_oc=Adrgu3uaQrJ_Dkq3i4ge8UpFGlzxUXAaXKrveLNM-TYt3U3Ec5U8-dFYlsQwd2RwHAM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afxo11BtsOe74CqiFeb7-Jk73U8EtRKZnWooWZqiveKJSw&amp;oe=69CAF7FC</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/656286692_18177043225390059_277424753296677871_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=8cZMaZLAuQMQ7kNvwEgZdtD&amp;_nc_oc=AdpmxaXAJ352mQVG4VkIdIpG8tSuIvOOv46Tc3inYzwXLntVndBBy2lbD8fnjwPeomc&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfxZrubGt3jSZNvKww7p39ZXP-HjmGecNG7z8QeNq-SBTA&amp;oe=69CB303C</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T21:00:00+0000</t>
@@ -170,7 +170,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwHhsUrK&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo2LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxJD7hvxVzxFfpO1z4MUDCiKr1LMSGjk-sqbySwBRdCFQ&amp;oe=69CAF247</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQNgruIy7wP9KChGkhyngWPyZzZH1qbasyzkJnfxl2fUIgleia2mrNHtsCSBaVsrQLiu16B8SycgTy3B8OpnVWk8.mp4?strext=1&amp;_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=KmCu2xgmeDYQ7kNvwFEsnXd&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzcwMDkxNjAzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo2LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODMsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=91fbca139006f4d3&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HTFhDX0NaTkgwb1hkR29EQU5PM2ZzU2FwWm8wYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc1NDUyNDU2NTU0MjFBQzBFQTg1RkU5Mjc0QzJCM0E3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWlqzhl_nJQBUCKAJDMywXQFTQAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afx_CT22Fhcyg96k5p7O-vmScAvDuseiFtoRvMjpzKZtqA&amp;oe=69CB2A87</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-20T12:33:26+0000</t>
@@ -187,7 +187,7 @@
 #RacismoAlgoritmico #InteligenciaArtificial #Diversidade #TecnologiaEtica #InclusãoDigital</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwEJPwXv&amp;_nc_oc=Adr8Bkbcj0W6hN0GJMl9Vr0sZtSNH-sz_B1u8znZbJePxTKD2-2rnTRZbBLsph3LDW0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afzow0E3L3dwI-HncXWPn9UX0PJR76d--BuW2dJIOc04yw&amp;oe=69CB1B04</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/654021471_18176775283390059_7494680639680233445_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DAkvzpzK1soQ7kNvwE79sXw&amp;_nc_oc=AdqFo_IGSzUbtjiy69XH2aXaUfhP8PyuYoLDT02mVQw5mZ09vDFs4OzOlohBJ2N2orw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfzVJo_vfuQ1ZtLppriQHSQMAp3Fh0Gp1a3Tukw9cYsttg&amp;oe=69CB1B04</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-18T16:51:12+0000</t>
@@ -206,7 +206,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwE2Jx3D&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxBNhbftIlN8XNGbnwsnvPfA_CBqfw9rN0MyjPHx4eNMg&amp;oe=69CB163F</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMtwLfryvo3rk5p4vfg1l7ZanDJY0NzJCvMOKltY71Xf0X9lcqKNTV2fk6p7-wnU-2dRfKjfxI3dRkRCbtf1DUP.mp4?strext=1&amp;_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;_nc_ohc=frEM0YGr5GoQ7kNvwFEoccd&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzY1NTIwNjIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjo5LCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=e01606748f16abc9&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HSGFCemlibnQ4Tlh5UE1JQUt6TDFKcTBnUkZvYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzEwNERFOUM5MTA1MkZCQzIzRTY1ODRBQUMyNzZEMDk1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWvNyOyt7JQBUCKAJDMywXQFeqn752yLQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxhCG3jAYwQPnUVpqwLlF-VSZx_jyhqSabgp0FYRXx10g&amp;oe=69CB163F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T21:00:00+0000</t>
@@ -231,7 +231,7 @@
 #Meta #InteligênciaArtificial #Tecnologia #Inovação #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwF6-6wZ&amp;_nc_oc=AdorHO76N-ZhyrGugR6DajxZeGVtiJk5uBBg98R20stgSbaaKepIxwbQn8ngiEAyHBc&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afywufrgv3V4UBbU2D121TRjOPMY-uJsCD-J1H5XhVvpVA&amp;oe=69CB2451</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/653587487_18176545963390059_2126542823829014999_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=elq8bCmQ7SAQ7kNvwGvSaid&amp;_nc_oc=Adr9uvI8j7Byt5PiShEmeWt7mUaT13nllmjWLIcy1zxKO3HZeATsXvffcWxFq3kEuiM&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfzVObSRFfBHFRwWV8FZm0M11QdM6fNyv9gCWN3VhHYriw&amp;oe=69CB2451</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-16T16:36:23+0000</t>
@@ -247,7 +247,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFCXR5k&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afwk-H14Dk-yde7XLUxFVsrUU_ymQ8pBkjuYJzrmVgwjhg&amp;oe=69CB21B9</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQMUUWPzeTKztu4J8hxDLexl-ZkBlEqZj_w1gCD5neNzYS3A7Ry9EZNiyKDBgQpWrWiAiE9v0rjtTP_Y4smNZH9w.mp4?strext=1&amp;_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=bP3RLXkHfb4Q7kNvwFWtOar&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzYwMDg5NDIzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxMiwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg3LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=29bd1a61866c3746&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HRV9pdlNib2RFMTREaDhEQVBwVXh4RFNhbEphYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0I0NDBEODEyM0Y4MERFMjdDREFDRTAwRDFDMTYxMkEwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWrJDH-77JQBUCKAJDMywXQFXK4UeuFHsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxZXxlaP12hvEnvPplXcFiBXXPhVFB-gHMgFPRTnj3lig&amp;oe=69CB21B9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T21:00:00+0000</t>
@@ -263,7 +263,7 @@
 #ECADigital #DesenvolvimentoDeSoftware #PrivacidadeDeDados #Ditec</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=dR7H77Di4aUQ7kNvwGTGWqY&amp;_nc_oc=AdqZ4fAWuV87a8CdWPeAnV3MO-Nezz53wdIiQC0icZ3OLYq-_0nwclAWH_WvB6ssrY8&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfyKtzs1a41DiZWVWpopaDAPJMh-fgmhxNRjoknsFtBihg&amp;oe=69CB0CF9</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/652004958_18176005099390059_6435756390161576649_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=7xkvpGgDdtwQ7kNvwGSCifC&amp;_nc_oc=AdqLTqVpIbgLrOKs-gyjhqnKOYHSZ5hxev4-I6QI7CmsSuBDtKCHfLnEoemHvgoXnXM&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afy9aXpTssYIrnmSCiVBuV5wP0Tcpjv9C8K_wkPlV19mAA&amp;oe=69CB0CF9</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-13T16:30:40+0000</t>
@@ -282,7 +282,7 @@
 #Tecnologia #IA #Hardware #SupplyChain Inovaç</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=2qJBgyE8haYQ7kNvwFY36Hh&amp;_nc_oc=AdrpmDAeHZpMqE6-Qpk4QoH5Ol4Hm-niZG5flr9mRhsZSkpDYAnjMXrbQWKeEIMNMUc&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afw7OBZOScnhPFG_64UMsAuXIPItYTuhfl6FDFh4mwnHmA&amp;oe=69CB09F7</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/650828855_18175823644390059_1150060007362356499_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=2qJBgyE8haYQ7kNvwGYc_Wl&amp;_nc_oc=Adq4FFbnuAKli7n6FXkDiPKPjRabUXGjQgM0yNbRL8srqBjl5L13P0yv4TnXm8ONb6M&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afwi3tWIe1Ngu4mTHGVC8VvN45FH1FPXVcFHllwlO9s9Kw&amp;oe=69CB09F7</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-12T15:04:46+0000</t>
@@ -299,7 +299,7 @@
 #Cibersegurança #ComunicatIBB #ProteçãoDeDados #SegurançaDigital #SegurançaFinanceira</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwEz1St9&amp;_nc_oc=AdqF9ZrlprWTkbazM94yho3fbDQ5yDg3s3ycB7yhexDFNhI6CAYVap0OwuKJHMR58Ac&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfzWc-2xhTDIcsGPKBF_TADTD7nJQL4jnFf5ElXDNyPWrQ&amp;oe=69CB00E8</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649500061_18175660729390059_3713546595178768698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=OtdsPH_ONZoQ7kNvwG2ei4Q&amp;_nc_oc=AdqrPrdROupMmfvPvAgBNhzCSsh1yDQfYtoLsnO6qNmpXKb_0mxVDjLieAt4p3a7Uyk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afz1N5rY9FSBZ_V4WvWjAdCgMimSeE7k8wVynogp6g9PiA&amp;oe=69CB3928</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T21:00:00+0000</t>
@@ -318,7 +318,7 @@
 #comunicatibb #AcessibilidadeDigital #InclusãoDigital #UX #Acessibilidade</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwGm9BXf&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afxb-F8uUFsiRs9KbabJl62q4bq9Gllu9k1k6JFPPclARw&amp;oe=69CAFA5E</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQP-cqXDy-zUMASBX_ASHawoLKHmPMThG9Y0-POlz8WdHUBk5MJbn5nNSeuTZ7NRz7Cf5RChlUcGC_-vw3TjRiqy.mp4?strext=1&amp;_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=B4X_vj25SScQ7kNvwEWbq6y&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzU2NjAwMzMzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxNSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjgyLCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=325bde5a8be2708c&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HREtWdHlZd1FaWFF5bjBGQU1nZW1KZnYtREJWYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzM1NEVBNzJCQTRBRjc0NjY4QUM4MUMwNTJBOEE4Qjk4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW18n906rJQBUCKAJDMywXQFSYAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_AfxywnuSgPmUTOh8XyZcGSjO5efUy3gvCZCErHTeLz6kew&amp;oe=69CB329E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T13:48:44+0000</t>
@@ -336,7 +336,7 @@
 #ColunistasBB #ComunicaTI #CompartilheConhecimento</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwEMr2X6&amp;_nc_oc=Adod9Flz7NH0iKPFoJPJpEaut5e7RU8IGkJ30rInj85cEmmGRV8EtoUS8WESHwG2b_I&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afy-cNXVs54NqET45SUtqXp4StVC4uCJwYQGTPyMv8KyuQ&amp;oe=69CB2048</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649231331_18175531624390059_3806228526867627159_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=PO74ePo9A_sQ7kNvwH-geKK&amp;_nc_oc=Adpb0x9qstPevX9oGUlZD8MjFJfrOQRRd0uKAI6tDWGk8hldO3KebMuii7bAGzeSf7M&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afwq9aYY44T_vkVZkGG9ceANyYhpnA05cpb2pvtRRpuERQ&amp;oe=69CB2048</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-10T17:21:57+0000</t>
@@ -361,7 +361,7 @@
 #GuildasBB #TecnologiaBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-2.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwFR4bAF&amp;_nc_oc=AdqsxrS-pxXltBL1v8tH_T99n2nG0jlNDxOdgqTQaEnS4CL-ARAzpOAfmdUIHKzQbaM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afx5N5w5WsFXGj3cnbc0Eswl_5WTbduEXGdp8R6JxWSqUQ&amp;oe=69CAF8AE</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/649539878_18175402141390059_2656838401666916360_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=I188QydO5F0Q7kNvwEvAAiO&amp;_nc_oc=AdpM1HYFKWD97nQi0hqst34cx03dshH_Bwn6kJD-q2OCJHCrJd0z0m0YypSOdKW5fHk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afxyla2Ihu-AkZ3xTfdtouoqZZ5Z8zBAjDFKBoUadsuzqw&amp;oe=69CB30EE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-09T13:59:40+0000</t>
@@ -378,7 +378,7 @@
 Feliz Dia Internacional das Mulheres. 💙💛</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwGq76mc&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afxr-0js-8fLvzwIcIaETJqU-ih97wPIG7DZyNry2-scXg&amp;oe=69CB2684</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/o1/v/t16/f2/m69/AQOvoIbQFxM-_KL8abfwbJ_Ynhp48t57vDr2hkc2BWAk23zvhK3t1rfcLnKHpmYfOBnsybkgKkz6gRtYB7SYqXcR.mp4?strext=1&amp;_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;_nc_ohc=n7H1z41V6qMQ7kNvwHHjtWv&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTgxNzUxMTU4NjkzOTAwNTksImFzc2V0X2FnZV9kYXlzIjoxOSwidmlfdXNlY2FzZV9pZCI6MTAwOTksImR1cmF0aW9uX3MiOjg2LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=6c2dd3d9b03c1994&amp;_nc_vs=HBksFQIYOnBhc3N0aHJvdWdoX2V2ZXJzdG9yZS9HR1lTY1NhbnF2T0tYMkFKQUYyT2ktNlVQNlEwYnNwVEFRQUYVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EzNEJCOUJCOUQ1RDMzNUMxNjMyNkI4NUY1MzQyODk2X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbWk6zS_YrJQBUCKAJDMywXQFWu6XjU_fQYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;edm=AM6HXa8EAAAA&amp;_nc_zt=28&amp;oh=00_Afyj1sff0pQlDYLy35QbjtYnhf8yeF-nEshmkwODM1bPdA&amp;oe=69CB2684</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-06T20:47:29+0000</t>
@@ -395,7 +395,7 @@
 #InteligenciaArtificial #Sustentabilidade #Tecnologia #IAVerde #Inovacao ComunicaTI</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwG-jFz1&amp;_nc_oc=Adone5H7vvQ3bOB5OLytlaF8pAjb8MCUVLghGiZj1YGJM1je4LItBM-iGWBW9AP0lks&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfxHACEiEuM-nnUcoNECFRh_2PR6p67EYrBMOYyXC7awlw&amp;oe=69CB0C5F</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/645813711_18174885565390059_3848023100434768088_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=mc5tyR7iIRMQ7kNvwHtHcVZ&amp;_nc_oc=Adrh6FbO1YYCw24eVYIr598K0bi0LQbolndYH5Rw5J0_vgtMdrViOmsB_Ge1N-ImIWw&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afy3k9vSSh2vNSWdTlsIVwk-fOLThFzy4StOR6D1oxEufA&amp;oe=69CB0C5F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-04T17:32:16+0000</t>
@@ -430,7 +430,7 @@
 Salve na agenda e participe! 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwFJygVk&amp;_nc_oc=AdrTrYtnspIxAa8m4d9DNfeQz53JXUanNBpT9w4G_Bp8wNUmC9EOZXWM2ZnSQJCaoUU&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwMZatKY0DaLGRiP44zTNA4Gad-iqoupTXUawdMbdLnaQ&amp;oe=69CAF2AE</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/642482132_18174793153390059_8090012253053192134_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=pH2-_veAoQgQ7kNvwE39MT5&amp;_nc_oc=Adq-2-Di7KWIR6fEGMZBiMc3i8s22hnAc6RFwzXwdT944OJ3r9GR5x-xakUG1GCqd_g&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfxiA9wuFC9ddXtyBLenWmKRVBZrkmT16-QFlJjCb2gslQ&amp;oe=69CB2AEE</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T18:48:00+0000</t>
@@ -457,7 +457,7 @@
 #MulheresNaTI #Carreira #LiderançaFeminina #Mentoria</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwHm8VsV&amp;_nc_oc=Ado_OTnyavDtblpS_-u9-bmm5d2EjXhRL9UoJ6ftxnZfHkvYmOJQeGpii1cF5vD8r9g&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfztZ82jMlGn_L--0eWzT8zJnpc9tmIRcNlxTollBBGz1w&amp;oe=69CAF2CA</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/645715457_18174782533390059_7525829143724356139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=gtr04rQeFo8Q7kNvwHDtNYW&amp;_nc_oc=Adp00lOo2scaqwnnDbs2TtwNvh-c1G530DsnugwsMcQOcBu60FMe1bxOy0NmsaJcARI&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfwXK8b49bLai8awIrIUzUJR_XzfnW-e6g6Lwa8mPxonKQ&amp;oe=69CB2B0A</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-03T16:15:52+0000</t>
@@ -471,7 +471,7 @@
 #ComunicaTI #Ditec #BancoDoBrasil #SomosBB</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwGKHINr&amp;_nc_oc=AdqUO9j7c4OHp2Y2-Ri9nvlFvVRmb_g91-SFFg458Hg02JtqgACb3HUi2Kf4jIROkrM&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwLRcM1e83aWz8RuZkfa9wwlRcfWCauajASv6WuwhzTEw&amp;oe=69CB07E6</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/642120823_18174230902390059_8546419987294142714_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=meYhJoSxzqsQ7kNvwGNNjZB&amp;_nc_oc=AdoL3WbW24HsTopd8jbZuQ2JN_HCQ5K2bTnYKx3SdeQeoEUUWCqXxEccE-QILkn_4vk&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfzVyddxRPDvGyhpkFBgTPynzERyRVTYDTxGQ-TcJ_iuWQ&amp;oe=69CB4026</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-25T17:10:36+0000</t>
@@ -495,7 +495,7 @@
 #BankingTransformation #Inovação #TecnologiaBB #bancodobrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwF2khAw&amp;_nc_oc=Adr_c3l8Aub1MRQ-OkVlkc1EfMdUx26pYFxF4wP3RSWwZNeQhS2iKEsUlg3U00LT1Rg&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwBrknfAwDXF_GRSeOZtCnLur7jmbbz5Arm4lsEF829qQ&amp;oe=69CAFAB5</t>
+    <t xml:space="preserve">https://scontent-atl3-1.cdninstagram.com/v/t51.82787-15/640956969_18174074971390059_1322183891194334687_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=SV62svknKOwQ7kNvwF9ktX1&amp;_nc_oc=AdrEB_rVxjdP4X7GgkBGvVMwJe9UYVBeAZuOuX2oXD_GGMJGJ31X2435r8AbHQYxbQ8&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afw5tKhqOtGV0DFGZKfGQrAwIx3DJnNiUffrjfFN0gt95Q&amp;oe=69CB32F5</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-24T00:45:36+0000</t>
@@ -527,7 +527,7 @@
 #GuildasDaSemana #Tecnologia</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwFxV0sw&amp;_nc_oc=AdoMS_J0_mrvMantjjnYqoSo12L7Vn4LxOq5D7uvdjyGvPnwDfA67RhmWqvvGKKdUMI&amp;_nc_zt=23&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfxZ65dRVAMr3tUYheTIg76zvGAG0pNFoQnRSUaNFLV7bQ&amp;oe=69CB165E</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/640912237_18174027721390059_5013319922840554120_n.heic?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=DGhs_VaYERgQ7kNvwH_jtn0&amp;_nc_oc=Adr4uf6b5oM6lxyxgY2Psj-gOTqLpHsrtgV7RdehJRLC7CFaDXir0P_VQl591QqwTNY&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afzx4gG6GsuSLXObRofjiburcKCNd7ylFq7aR3ghPzL1vQ&amp;oe=69CB165E</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-23T12:27:17+0000</t>
@@ -545,7 +545,7 @@
 #MeninasNaCiência #MulheresNaCiência #MeninasNaCiência #WomenInScience #Inovação</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwGPsul-&amp;_nc_oc=Adq2C2spjOtrtJjpKUaBn7Hhl-PAonwK7lPW6oWvdM-sQqigGdujVpbDoe_2u0WgLH0&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_AfwOihKVaZEF0oTotcHhIj7Ys2Quz2Fi6qJt-Th9efIBJQ&amp;oe=69CB1D8F</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/631838855_18172908409390059_6347656520415793303_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiRkVFRC5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=6PVB-JugRSkQ7kNvwFM0YjT&amp;_nc_oc=Ado9W0B8XDwMErTxQ9RJPBEzAads0PaiOALevGOBtc_AMW3erP4NUEX2BCjTJ-7-qNU&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_Afx9EJJ1-eKZxcuYzJFdJyjYrXQUFIZmaKVu8YkT_96VDA&amp;oe=69CB1D8F</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-11T13:46:50+0000</t>
@@ -567,7 +567,7 @@
 #GuildasDaSemana #Tecnologia #TI #Dados DividaTecnica Analytics IA BancoDoBrasil</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwF-YSqH&amp;_nc_oc=AdpGw4jb0E_cB4gxD_94K8p8cSpacCvezdCK0UHn3sA7mkgBYKyjvFiOKqbapU5c0kk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=ogTTAlC2cv_e6cd_AH3nPg&amp;oh=00_Afxx_0dyjNjPfPEswaFifIs_DfSoYagofo7HirHLL05gXA&amp;oe=69CB0712</t>
+    <t xml:space="preserve">https://scontent-atl3-2.cdninstagram.com/v/t51.82787-15/631302949_18172752532390059_7332008111931530737_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ccb=7-5&amp;_nc_sid=18de74&amp;efg=eyJlZmdfdGFnIjoiQ0FST1VTRUxfSVRFTS5iZXN0X2ltYWdlX3VybGdlbi5DMyJ9&amp;_nc_ohc=VwgJIqokIWsQ7kNvwFeV1YB&amp;_nc_oc=Adqby4E6JBA7IzyNoMKlpERlEh9QWNrLOXWPKSeLaSVtMz8ajh95Yxt1P7_Ln4H7p5w&amp;_nc_zt=23&amp;_nc_ht=scontent-atl3-2.cdninstagram.com&amp;edm=AM6HXa8EAAAA&amp;_nc_gid=rCBnWiHv8YHhY-3aBa1Lbg&amp;oh=00_AfyFMJXQRuGe8CTVnnftF15Kruq84U3G_nE61gFpunJc2Q&amp;oe=69CB3F52</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-09T15:36:07+0000</t>
